--- a/product list.xlsx
+++ b/product list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\macbello\Desktop\Nithin\Account\Purchase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3284501F-AF85-4E7E-A5BC-2F07FDD8A291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD96A91-DEF7-4829-8FB6-B3E2B52D4661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{196A3D5A-6638-496F-9065-39B375FBF2B9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -164,13 +164,37 @@
     <t xml:space="preserve">KEUNE CARE DERMA ACTIVATE LOTION 75 ML </t>
   </si>
   <si>
-    <t>MAJESTIC REPL SHAMPOO 300ML</t>
-  </si>
-  <si>
-    <t>MAJESTIC REPL CONDTIONER 300ML</t>
-  </si>
-  <si>
     <t>tax rate</t>
+  </si>
+  <si>
+    <t>HSN CODE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG SUN SCREEN LOTION SPF15 </t>
+  </si>
+  <si>
+    <t>KRONE PRO ANTI-DANDRFF TONIC 100 ML</t>
+  </si>
+  <si>
+    <t>KRONE ANTI-DANDRFF CONTRL CLANSER 200 ML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG SUN SCREEN SPF30 55ML </t>
+  </si>
+  <si>
+    <t>KRONE ANTI DANDRUFF CONTROL MASQUE 500 ML</t>
+  </si>
+  <si>
+    <t>KEUNE CARE VITAL NUTRITION MASK 250 ML</t>
+  </si>
+  <si>
+    <t>MK MAJESTIC REPL SHAMPOO 300ML</t>
+  </si>
+  <si>
+    <t>MK MAJESTIC REPL CONDTIONER 300ML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      </t>
   </si>
 </sst>
 </file>
@@ -201,7 +225,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -211,6 +235,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -255,29 +285,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -612,635 +662,866 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A937DD98-2807-42C2-8BEE-00B32B8B411E}">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="60.21875" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" customWidth="1"/>
-    <col min="4" max="4" width="7.44140625" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.88671875" customWidth="1"/>
+    <col min="5" max="5" width="7.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C2" s="3">
         <v>660</v>
       </c>
-      <c r="C2" s="2">
+      <c r="D2" s="2">
         <v>12</v>
       </c>
-      <c r="D2" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C3" s="3">
         <v>660</v>
       </c>
-      <c r="C3" s="2">
+      <c r="D3" s="2">
         <v>12</v>
       </c>
-      <c r="D3" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E3" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C4" s="3">
         <v>880</v>
       </c>
-      <c r="C4" s="2">
+      <c r="D4" s="2">
         <v>3</v>
       </c>
-      <c r="D4" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E4" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C5" s="3">
         <v>880</v>
       </c>
-      <c r="C5" s="2">
+      <c r="D5" s="2">
         <v>4</v>
       </c>
-      <c r="D5" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="E5" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="13">
+        <v>33051090</v>
+      </c>
+      <c r="C6" s="14">
         <v>1513</v>
       </c>
-      <c r="C6" s="2">
-        <f>5+12</f>
-        <v>17</v>
-      </c>
-      <c r="D6" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="13">
+        <v>23</v>
+      </c>
+      <c r="E6" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C7" s="3">
         <v>1700</v>
       </c>
-      <c r="C7" s="2">
-        <f>5+12</f>
+      <c r="D7" s="2">
+        <v>23</v>
+      </c>
+      <c r="E7" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C8" s="3">
+        <v>855</v>
+      </c>
+      <c r="D8" s="2">
+        <v>3</v>
+      </c>
+      <c r="E8" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="13">
+        <v>33051090</v>
+      </c>
+      <c r="C9" s="14">
+        <v>375</v>
+      </c>
+      <c r="D9" s="13">
+        <v>20</v>
+      </c>
+      <c r="E9" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="2">
+        <v>330510</v>
+      </c>
+      <c r="C10" s="3">
+        <v>500</v>
+      </c>
+      <c r="D10" s="2">
+        <v>20</v>
+      </c>
+      <c r="E10" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="2">
+        <v>33042000</v>
+      </c>
+      <c r="C11" s="3">
+        <v>405</v>
+      </c>
+      <c r="D11" s="2">
+        <v>10</v>
+      </c>
+      <c r="E11" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C12" s="3">
+        <v>315</v>
+      </c>
+      <c r="D12" s="2">
+        <v>12</v>
+      </c>
+      <c r="E12" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C13" s="3">
+        <v>315</v>
+      </c>
+      <c r="D13" s="2">
+        <v>11</v>
+      </c>
+      <c r="E13" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="2">
+        <v>33049910</v>
+      </c>
+      <c r="C14" s="3">
+        <v>375</v>
+      </c>
+      <c r="D14" s="2">
+        <v>5</v>
+      </c>
+      <c r="E14" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="2">
+        <v>33042000</v>
+      </c>
+      <c r="C15" s="3">
+        <v>335</v>
+      </c>
+      <c r="D15" s="2">
+        <v>5</v>
+      </c>
+      <c r="E15" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="13">
+        <v>33059090</v>
+      </c>
+      <c r="C16" s="14">
+        <v>1465</v>
+      </c>
+      <c r="D16" s="13">
+        <v>5</v>
+      </c>
+      <c r="E16" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1650</v>
+      </c>
+      <c r="D17" s="2">
+        <v>5</v>
+      </c>
+      <c r="E17" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C18" s="3">
+        <v>3200</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2</v>
+      </c>
+      <c r="E18" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="13">
+        <v>33051090</v>
+      </c>
+      <c r="C19" s="14">
+        <v>2200</v>
+      </c>
+      <c r="D19" s="13">
+        <v>3</v>
+      </c>
+      <c r="E19" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C20" s="3">
+        <v>4600</v>
+      </c>
+      <c r="D20" s="4">
+        <v>5</v>
+      </c>
+      <c r="E20" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C21" s="3">
+        <v>980</v>
+      </c>
+      <c r="D21" s="4">
+        <v>3</v>
+      </c>
+      <c r="E21" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="3">
-        <v>315</v>
-      </c>
-      <c r="C8" s="2">
+      <c r="B22" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C22" s="3">
+        <v>525</v>
+      </c>
+      <c r="D22" s="4">
         <v>2</v>
       </c>
-      <c r="D8" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="3">
-        <v>315</v>
-      </c>
-      <c r="C9" s="2">
+      <c r="E22" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="D23" s="2">
         <v>1</v>
       </c>
-      <c r="D9" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="3">
-        <v>375</v>
-      </c>
-      <c r="C10" s="2">
-        <v>5</v>
-      </c>
-      <c r="D10" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="3">
-        <v>1465</v>
-      </c>
-      <c r="C11" s="2">
-        <v>5</v>
-      </c>
-      <c r="D11" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="3">
-        <v>1650</v>
-      </c>
-      <c r="C12" s="2">
-        <v>5</v>
-      </c>
-      <c r="D12" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="3">
-        <v>3200</v>
-      </c>
-      <c r="C13" s="2">
+      <c r="E23" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C25" s="3">
+        <v>2600</v>
+      </c>
+      <c r="D25" s="2">
+        <v>3</v>
+      </c>
+      <c r="E25" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C26" s="6">
+        <v>2150</v>
+      </c>
+      <c r="D26" s="5">
+        <v>40</v>
+      </c>
+      <c r="E26" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="10"/>
+      <c r="C27" s="11">
+        <v>340</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="2">
+        <v>33049990</v>
+      </c>
+      <c r="C28" s="3">
+        <v>550</v>
+      </c>
+      <c r="D28" s="2">
+        <v>5</v>
+      </c>
+      <c r="E28" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="2">
+        <v>33049990</v>
+      </c>
+      <c r="C29" s="3">
+        <v>350</v>
+      </c>
+      <c r="D29" s="2">
+        <v>5</v>
+      </c>
+      <c r="E29" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="2">
+        <v>330499</v>
+      </c>
+      <c r="C30" s="3">
+        <v>550</v>
+      </c>
+      <c r="D30" s="2">
+        <v>5</v>
+      </c>
+      <c r="E30" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="2">
+        <v>33049990</v>
+      </c>
+      <c r="C31" s="3">
+        <v>430</v>
+      </c>
+      <c r="D31" s="2">
+        <v>5</v>
+      </c>
+      <c r="E31" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="2">
+        <v>330499</v>
+      </c>
+      <c r="C32" s="3">
+        <v>570</v>
+      </c>
+      <c r="D32" s="2">
+        <v>5</v>
+      </c>
+      <c r="E32" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" s="2">
+        <v>330499</v>
+      </c>
+      <c r="C33" s="3">
+        <v>625</v>
+      </c>
+      <c r="D33" s="2">
+        <v>5</v>
+      </c>
+      <c r="E33" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" s="2">
+        <v>330499</v>
+      </c>
+      <c r="C34" s="3">
+        <v>695</v>
+      </c>
+      <c r="D34" s="2">
+        <v>6</v>
+      </c>
+      <c r="E34" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="2">
+        <v>330499</v>
+      </c>
+      <c r="C35" s="3">
+        <v>2800</v>
+      </c>
+      <c r="D35" s="2">
         <v>2</v>
       </c>
-      <c r="D13" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="3">
+      <c r="E35" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" s="13">
+        <v>33051090</v>
+      </c>
+      <c r="C36" s="14">
+        <v>1740</v>
+      </c>
+      <c r="D36" s="13">
+        <v>2</v>
+      </c>
+      <c r="E36" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="2">
+        <v>330499</v>
+      </c>
+      <c r="C37" s="3">
+        <v>450</v>
+      </c>
+      <c r="D37" s="2">
+        <v>6</v>
+      </c>
+      <c r="E37" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="2">
+        <v>330499</v>
+      </c>
+      <c r="C38" s="3">
+        <v>650</v>
+      </c>
+      <c r="D38" s="2">
+        <v>4</v>
+      </c>
+      <c r="E38" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" s="2">
+        <v>330499</v>
+      </c>
+      <c r="C39" s="3">
+        <v>600</v>
+      </c>
+      <c r="D39" s="2">
+        <v>4</v>
+      </c>
+      <c r="E39" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" s="2">
+        <v>330499</v>
+      </c>
+      <c r="C40" s="3">
+        <v>1500</v>
+      </c>
+      <c r="D40" s="2">
+        <v>4</v>
+      </c>
+      <c r="E40" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" s="2">
+        <v>33049990</v>
+      </c>
+      <c r="C41" s="3">
+        <v>3480</v>
+      </c>
+      <c r="D41" s="2">
+        <v>2</v>
+      </c>
+      <c r="E41" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" s="13">
+        <v>33051090</v>
+      </c>
+      <c r="C42" s="14">
+        <v>3825</v>
+      </c>
+      <c r="D42" s="13">
+        <v>1</v>
+      </c>
+      <c r="E42" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C43" s="3">
+        <v>4100</v>
+      </c>
+      <c r="D43" s="2">
+        <v>1</v>
+      </c>
+      <c r="E43" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="13">
+        <v>33051090</v>
+      </c>
+      <c r="C44" s="14">
+        <v>1975</v>
+      </c>
+      <c r="D44" s="13">
+        <v>3</v>
+      </c>
+      <c r="E44" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="D45" s="2">
+        <v>3</v>
+      </c>
+      <c r="E45" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" s="13">
+        <v>33051090</v>
+      </c>
+      <c r="C46" s="14">
+        <v>1695</v>
+      </c>
+      <c r="D46" s="13">
+        <v>2</v>
+      </c>
+      <c r="E46" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C47" s="3">
+        <v>1800</v>
+      </c>
+      <c r="D47" s="2">
+        <v>2</v>
+      </c>
+      <c r="E47" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" s="13">
+        <v>33051090</v>
+      </c>
+      <c r="C48" s="14">
+        <v>1850</v>
+      </c>
+      <c r="D48" s="13">
+        <v>2</v>
+      </c>
+      <c r="E48" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C49" s="3">
         <v>2200</v>
       </c>
-      <c r="C14" s="2">
-        <v>3</v>
-      </c>
-      <c r="D14" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="3">
-        <v>4600</v>
-      </c>
-      <c r="C15" s="4">
-        <v>5</v>
-      </c>
-      <c r="D15" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="3">
-        <v>980</v>
-      </c>
-      <c r="C16" s="4">
-        <v>3</v>
-      </c>
-      <c r="D16" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="3">
-        <v>525</v>
-      </c>
-      <c r="C17" s="4">
+      <c r="D49" s="2">
         <v>2</v>
       </c>
-      <c r="D17" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="3">
-        <v>4200</v>
-      </c>
-      <c r="C18" s="2">
+      <c r="E49" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="2">
+        <v>33059090</v>
+      </c>
+      <c r="C50" s="3">
+        <v>2200</v>
+      </c>
+      <c r="D50" s="2">
         <v>1</v>
       </c>
-      <c r="D18" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="3">
-        <v>1800</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1</v>
-      </c>
-      <c r="D19" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="3">
-        <v>340</v>
-      </c>
-      <c r="C20" s="2">
-        <v>48</v>
-      </c>
-      <c r="D20" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="3">
-        <v>550</v>
-      </c>
-      <c r="C21" s="2">
-        <v>5</v>
-      </c>
-      <c r="D21" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="3">
-        <v>350</v>
-      </c>
-      <c r="C22" s="2">
-        <v>5</v>
-      </c>
-      <c r="D22" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="3">
-        <v>550</v>
-      </c>
-      <c r="C23" s="2">
-        <v>5</v>
-      </c>
-      <c r="D23" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="3">
-        <v>430</v>
-      </c>
-      <c r="C24" s="2">
-        <v>5</v>
-      </c>
-      <c r="D24" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="3">
-        <v>570</v>
-      </c>
-      <c r="C25" s="2">
-        <v>5</v>
-      </c>
-      <c r="D25" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="3">
-        <v>625</v>
-      </c>
-      <c r="C26" s="2">
-        <v>5</v>
-      </c>
-      <c r="D26" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="3">
-        <v>695</v>
-      </c>
-      <c r="C27" s="2">
-        <v>6</v>
-      </c>
-      <c r="D27" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="3">
-        <v>2800</v>
-      </c>
-      <c r="C28" s="2">
-        <v>2</v>
-      </c>
-      <c r="D28" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="3">
-        <v>1740</v>
-      </c>
-      <c r="C29" s="2">
-        <v>2</v>
-      </c>
-      <c r="D29" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="3">
-        <v>450</v>
-      </c>
-      <c r="C30" s="2">
-        <v>6</v>
-      </c>
-      <c r="D30" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="3">
-        <v>650</v>
-      </c>
-      <c r="C31" s="2">
-        <v>4</v>
-      </c>
-      <c r="D31" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" s="3">
-        <v>600</v>
-      </c>
-      <c r="C32" s="2">
-        <v>4</v>
-      </c>
-      <c r="D32" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="3">
-        <v>1500</v>
-      </c>
-      <c r="C33" s="2">
-        <v>4</v>
-      </c>
-      <c r="D33" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="3">
-        <v>3480</v>
-      </c>
-      <c r="C34" s="2">
-        <v>2</v>
-      </c>
-      <c r="D34" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" s="3">
-        <v>3825</v>
-      </c>
-      <c r="C35" s="2">
-        <v>1</v>
-      </c>
-      <c r="D35" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" s="3">
-        <v>4100</v>
-      </c>
-      <c r="C36" s="2">
-        <v>1</v>
-      </c>
-      <c r="D36" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3">
-        <v>1850</v>
-      </c>
-      <c r="C37" s="2">
-        <v>2</v>
-      </c>
-      <c r="D37" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="3">
-        <v>2200</v>
-      </c>
-      <c r="C38" s="2">
-        <v>2</v>
-      </c>
-      <c r="D38" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="3">
-        <v>2200</v>
-      </c>
-      <c r="C39" s="2">
-        <v>1</v>
-      </c>
-      <c r="D39" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="3">
-        <v>1975</v>
-      </c>
-      <c r="C40" s="2">
-        <v>3</v>
-      </c>
-      <c r="D40" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="3">
-        <v>2100</v>
-      </c>
-      <c r="C41" s="2">
-        <v>3</v>
-      </c>
-      <c r="D41" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="6">
-        <v>2150</v>
-      </c>
-      <c r="C42" s="5">
-        <v>10</v>
-      </c>
-      <c r="D42" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3">
-        <v>1695</v>
-      </c>
-      <c r="C43" s="2">
-        <v>2</v>
-      </c>
-      <c r="D43" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="3">
-        <v>1800</v>
-      </c>
-      <c r="C44" s="2">
-        <v>2</v>
-      </c>
-      <c r="D44" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="46" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+      <c r="E50" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
